--- a/data/02_Daily_Sheets/Expressions_2026-05-29.xlsx
+++ b/data/02_Daily_Sheets/Expressions_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENG-20260529-001</t>
+          <t>ENG-20260529-096</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lay out</t>
+          <t>shut someone/something out</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -491,29 +491,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>/leɪ aʊt/</t>
+          <t>/ʃʌt aʊt/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>계획, 요구사항, 사실 등을 명확하게 제시하거나 설명하다</t>
+          <t>~을 배제하다, 시장 진입을 막다</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Trump's Truth Social statement left unclear which of his conditions are already part of a deal that negotiators are working on to pause the U.S.-Iran war. Trump lays out Iran deal demands, says he's about to make 'final determination'.</t>
+          <t>Mercedes-Benz may be shut out of U.S. market under bill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The CEO will lay out the company's new strategy for the next fiscal year at the upcoming board meeting.</t>
+          <t>The new regulations could shut out smaller companies from competing.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ENG-20260529-002</t>
+          <t>ENG-20260529-097</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>work on</t>
+          <t>apply to</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,29 +538,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>/wɜːrk ɒn/</t>
+          <t>/əˈplaɪ tuː/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>무언가를 개선하거나 완성하기 위해 노력하다, 연구하다</t>
+          <t>(규칙, 법 등이) ~에 적용되다, 해당하다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Trump's Truth Social statement left unclear which of his conditions are already part of a deal that negotiators are working on to pause the U.S.-Iran war.</t>
+          <t>exemptions in the legislation would not apply.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>We are currently working on a new software update to fix the bugs reported by users.</t>
+          <t>The new tax rules will apply to all citizens, regardless of income.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ENG-20260529-003</t>
+          <t>ENG-20260529-098</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>diverge from</t>
+          <t>lean into</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,29 +585,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>/daɪˈvɜːrdʒ frɒm/</t>
+          <t>/liːn ˈɪntuː/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>기존의 계획, 의견, 경로 등에서 벗어나다, 달라지다</t>
+          <t>~에 기대다, (어려움에) 적극적으로 맞서다</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SpaceX skeptics have added reason for concern after Musk comments diverge from IPO filing.</t>
+          <t>force consumers to raid their savings and lean more into debt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The committee's final recommendations diverged significantly from the initial proposal.</t>
+          <t>Instead of avoiding the challenge, you should lean into it and learn from the experience.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENG-20260529-004</t>
+          <t>ENG-20260529-099</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,39 +622,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>shut someone out of</t>
+          <t>pose a risk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>/ʃʌt ˌsʌmwʌn aʊt ɒv/</t>
+          <t>/poʊz ə rɪsk/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>어떤 기회, 시장, 장소 등에서 누군가를 배제하거나 참여를 막다</t>
+          <t>위험을 제기하다</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mercedes-Benz may be shut out of U.S. market under bill aimed at Chinese automaker ownership.</t>
+          <t>posing a risk the market hasn't priced in.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>They tried to shut us out of the negotiations, but we found a way to participate.</t>
+          <t>Driving without a seatbelt can pose a serious risk to your safety.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENG-20260529-005</t>
+          <t>ENG-20260529-100</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -669,39 +669,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>aim at</t>
+          <t>claim a benefit</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>/eɪm æt/</t>
+          <t>/kleɪm ə ˈbɛnɪfɪt/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>특정 목표나 대상을 향하다, 겨냥하다</t>
+          <t>혜택을 신청하다/받다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mercedes-Benz may be shut out of U.S. market under bill aimed at Chinese automaker ownership.</t>
+          <t>Roth IRA owners may need a second retirement account to claim the new Saver's Match</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The new marketing campaign is primarily aimed at younger consumers.</t>
+          <t>You might be eligible to claim unemployment benefits if you lose your job.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENG-20260529-006</t>
+          <t>ENG-20260529-101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>raid savings</t>
+          <t>deliver on time</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -726,29 +726,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>/reɪd ˈseɪvɪŋz/</t>
+          <t>/dɪˈlɪvər ɒn taɪm/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>비상금이나 저축한 돈을 꺼내 쓰다</t>
+          <t>정시에 배달하다/이행하다</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
+          <t>Only three-quarters of first class mail delivered on time</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Many families had to raid their savings to cover unexpected medical bills during the pandemic.</t>
+          <t>It's crucial for us to deliver the project on time and within budget.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENG-20260529-007</t>
+          <t>ENG-20260529-102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,44 +758,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lean into debt</t>
+          <t>be set to</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>/liːn ˈɪntuː dɛt/</t>
+          <t>/biː sɛt tuː/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>빚을 더 많이 지게 되다, 빚에 의존하게 되다</t>
+          <t>~할 예정이다, ~할 준비가 되어 있다</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
+          <t>the number of 16 to 24-year-olds out of work, education or training is set to rise</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Without a steady income, many small businesses were forced to lean into debt to keep their operations going.</t>
+          <t>The new product is set to launch next month.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENG-20260529-008</t>
+          <t>ENG-20260529-103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>suffer a setback</t>
+          <t>struggle to do something</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -820,29 +820,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>/ˈsʌfər ə ˈsɛtbæk/</t>
+          <t>/ˈstrʌɡl̩ tuː duː ˈsʌmθɪŋ/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>차질을 겪다, 좌절을 경험하다</t>
+          <t>~하는 데 어려움을 겪다, 고군분투하다</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jeff Bezos' rocket maker suffered a setback on Thursday as its New Glenn rocket went up in flames.</t>
+          <t>young people who are struggling to find work</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The project suffered a major setback when the lead engineer resigned unexpectedly.</t>
+          <t>He's struggling to learn a new language while working full-time.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENG-20260529-009</t>
+          <t>ENG-20260529-104</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,44 +852,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>go up in flames</t>
+          <t>bar someone from doing something</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>/ɡoʊ ʌp ɪn fleɪmz/</t>
+          <t>/bɑːr ˈsʌmwʌn frɒm ˈduːɪŋ ˈsʌmθɪŋ/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>불에 타다; 계획이나 노력이 완전히 실패하다, 수포로 돌아가다</t>
+          <t>누군가가 ~하는 것을 금지하다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Jeff Bezos' rocket maker suffered a setback on Thursday as its New Glenn rocket went up in flames.</t>
+          <t>Federal law bars printing images of living people on US currency</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>All their hard work went up in flames when the server crashed and they lost all the data.</t>
+          <t>The club decided to bar him from entering after his previous behavior.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENG-20260529-010</t>
+          <t>ENG-20260529-105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>return to the public market</t>
+          <t>make an exception</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -914,29 +914,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>/rɪˈtɜːrn tuː ðə ˈpʌblɪk ˈmɑːrkɪt/</t>
+          <t>/meɪk ən ɪkˈsɛpʃn̩/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>상장 폐지 후 다시 주식시장에 상장하다</t>
+          <t>예외를 두다/인정하다</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Dell reported its fastest pace of revenue growth since returning to the public market in 2018.</t>
+          <t>Trump allies in Congress are moving to make an exception.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>After several years of private ownership, the tech giant plans to return to the public market next year.</t>
+          <t>We usually don't allow pets, but we can make an exception for service animals.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ENG-20260529-011</t>
+          <t>ENG-20260529-106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>face criticism</t>
+          <t>explode into flames</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -961,29 +961,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>/feɪs ˈkrɪtɪˌsɪzəm/</t>
+          <t>/ɪkˈsploʊd ˈɪntuː fleɪmz/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>비난을 받다, 비판에 직면하다</t>
+          <t>폭발하며 불길에 휩싸이다</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The DOJ has faced strong criticism for the creation of a $1.8 Anti-Weaponization Fund.</t>
+          <t>Blue Origin rocket explodes into huge ball of flame</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>The government is currently facing strong criticism over its handling of the economic crisis.</t>
+          <t>The old factory building suddenly exploded into flames.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ENG-20260529-012</t>
+          <t>ENG-20260529-107</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>launch a review</t>
+          <t>have a rough day</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>/lɔːntʃ ə rɪˈvjuː/</t>
+          <t>/hæv ə rʌf deɪ/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>조사나 검토를 시작하다</t>
+          <t>힘든 하루를 보내다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
+          <t>Jeff Bezos, who founded Blue Origin, said it was a 'very rough day'.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>The university decided to launch an independent review into the allegations of academic misconduct.</t>
+          <t>I had a really rough day at work; everything seemed to go wrong.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENG-20260529-013</t>
+          <t>ENG-20260529-108</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1040,44 +1040,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ahead of schedule</t>
+          <t>get together</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>/əˈhɛd ɒv ˈʃɛdʒuːl/</t>
+          <t>/ɡɛt təˈɡɛðər/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>예정보다 일찍, 기한보다 빨리</t>
+          <t>만나다, 함께하다; (연인 관계가) 시작되다</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
+          <t>I was always rooting for you two kids to get together.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>The construction project was completed two weeks ahead of schedule, much to everyone's relief.</t>
+          <t>Let's get together for coffee sometime next week.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENG-20260529-014</t>
+          <t>ENG-20260529-109</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1087,44 +1087,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>face a hurdle</t>
+          <t>be about the money</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>/feɪs ə ˈhɜːrdl/</t>
+          <t>/biː əˈbaʊt ðə ˈmʌni/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>난관에 부딪히다, 장애물에 직면하다</t>
+          <t>돈이 문제다, 돈 때문에 하는 것이다</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Roth IRA owners may face a hurdle to get the money.</t>
+          <t>this isn't about the money.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Startups often face many hurdles in their early stages, from funding to market acceptance.</t>
+          <t>For some, success is about passion, but for others, it's just about the money.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ENG-20260529-015</t>
+          <t>ENG-20260529-110</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1134,44 +1134,44 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>be on track to</t>
+          <t>on top of</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>/bi ɒn træk tuː/</t>
+          <t>/ɒn tɒp ɒv/</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>순조롭게 진행되어 ~할 것으로 예상되다, ~를 달성할 궤도에 오르다</t>
+          <t>~뿐만 아니라, ~위에 덧붙여</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Royal Mail says its service is improving and that it is on track to hit the regulator Ofcom's reduced targets.</t>
+          <t>And that's on top of the yearly bonus structure you mentioned earlier?</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>The company is on track to exceed its sales targets for the third quarter.</t>
+          <t>On top of working full-time, she's also studying for her master's degree.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ENG-20260529-016</t>
+          <t>ENG-20260529-111</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1181,44 +1181,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ease pressure</t>
+          <t>have the wrong guy</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>/iːz ˈprɛʃər/</t>
+          <t>/hæv ðə rɒŋ ɡaɪ/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>압력, 부담, 긴장 등을 완화시키다</t>
+          <t>사람을 잘못 찾았다, 오해하다</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tom Kerridge, Yotam Ottolenghi, Ravneet Gill and Simon Rogan told BBC Newsnight VAT should be halved to ease mounting pressure on the hospitality industry.</t>
+          <t>I'm telling you, you've got the wrong guy!</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>The government implemented new policies to ease pressure on small businesses struggling with rising costs.</t>
+          <t>If you think I'm the one who stole your wallet, you've got the wrong guy.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ENG-20260529-017</t>
+          <t>ENG-20260529-112</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1228,44 +1228,44 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>move to make an exception</t>
+          <t>slam down the phone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>/muːv tuː meɪk æn ɪkˈsɛpʃən/</t>
+          <t>/slæm daʊn ðə foʊn/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>예외를 두는 조치를 취하다, 예외를 만들려 하다</t>
+          <t>전화를 쾅 내려놓다</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Federal law bars printing images of living people on US currency, but Trump allies in Congress are moving to make an exception.</t>
+          <t>(slams the phone down)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The council is considering moving to make an exception for historical buildings in the new zoning laws.</t>
+          <t>She was so angry that she slammed down the phone after the argument.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ENG-20260529-018</t>
+          <t>ENG-20260529-113</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>build on</t>
+          <t>show someone around</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1290,29 +1290,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>/bɪld ɒn/</t>
+          <t>/ʃoʊ ˈsʌmwʌn əˈraʊnd/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>기존의 성공, 경험, 기반 등을 바탕으로 발전시키다</t>
+          <t>~에게 구경시켜주다, 안내하다</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BMW is introducing humanoid robots to a car plant in Europe, building on similar projects in the US.</t>
+          <t>Chandler's new window office, he is showing Phoebe around.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>We plan to build on the success of our previous product launch with an even stronger marketing campaign.</t>
+          <t>When you visit, I'll show you around the city.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENG-20260529-019</t>
+          <t>ENG-20260529-114</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>retaliate against</t>
+          <t>check out</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1337,29 +1337,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>/rɪˈtæliˌeɪt əˈɡɛnst/</t>
+          <t>/tʃɛk aʊt/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>~에 대해 보복하거나 앙갚음하다</t>
+          <t>~을 확인하다, 조사하다; (무언가를) 보다/경험하다</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sales of the fruity liqueur popular with Canadian students had plummetted north of the border as provinces retaliated against Trump tariffs.</t>
+          <t>Check this out, look at this.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>The country vowed to retaliate against any cyberattacks on its critical infrastructure.</t>
+          <t>You should check out that new cafe downtown; it's really good.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ENG-20260529-020</t>
+          <t>ENG-20260529-115</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1369,44 +1369,44 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>explode into a ball of flame</t>
+          <t>come in</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>/ɪkˈsploʊd ˈɪntuː ə bɔːl ɒv fleɪm/</t>
+          <t>/kʌm ɪn/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>커다란 불꽃 덩어리로 폭발하다</t>
+          <t>(방 안으로) 들어오다</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Blue Origin rocket explodes into huge ball of flame on Florida launch pad.</t>
+          <t>Helen, could you come in here for a moment?</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>The old fireworks factory accidentally exploded into a ball of flame, causing widespread alarm.</t>
+          <t>Please come in and make yourself comfortable.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENG-20260529-021</t>
+          <t>ENG-20260529-116</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1421,39 +1421,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>fall in love with</t>
+          <t>that'll be all</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>/fɔːl ɪn lʌv wɪð/</t>
+          <t>/ðætɪl biː ɔːl/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>~와 사랑에 빠지다</t>
+          <t>그게 다예요, 더 필요 없어요</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>But I have to warn you; this may make me a better person and that is not the man you feel in love with!</t>
+          <t>Thank you Helen, that'll be all.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>They met at a friend's party and quickly fell in love with each other.</t>
+          <t>I'd like a coffee and a croissant, please. That'll be all.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENG-20260529-022</t>
+          <t>ENG-20260529-117</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1468,39 +1468,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lay out the ground rules</t>
+          <t>bail on someone/something</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>/leɪ aʊt ðə ɡraʊnd ruːlz/</t>
+          <t>/beɪl ɒn/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>기본 규칙이나 원칙을 명확히 설명하다</t>
+          <t>(약속을) 바람맞히다, ~을 저버리다</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Joey and Ross are laying out the ground rules for the maid of honor auditions to Rachel and Phoebe.</t>
+          <t>Wendy bailed. I have no waitress.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Before we start the project, let's lay out the ground rules for communication and collaboration.</t>
+          <t>He bailed on our dinner plans at the last minute.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENG-20260529-023</t>
+          <t>ENG-20260529-118</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>score on a scale of</t>
+          <t>make plans</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1525,29 +1525,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>/skɔːr ɒn ə skeɪl ɒv/</t>
+          <t>/meɪk plænz/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>~의 척도로 점수를 매기다/평가하다</t>
+          <t>계획을 세우다</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>We’re gonna give you hypothetical maid of honor situations and you will be scored on a scale of 1 to 10.</t>
+          <t>I've made plans to walk around.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Participants were asked to score the meal on a scale of 1 to 5, with 5 being excellent.</t>
+          <t>We should make plans to go hiking this summer.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ENG-20260529-024</t>
+          <t>ENG-20260529-119</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>be up first</t>
+          <t>be there for someone</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1572,29 +1572,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>/bi ʌp fɜːrst/</t>
+          <t>/biː ðɛr fɔːr ˈsʌmwʌn/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>첫 번째 순서이다, 먼저 시작하다</t>
+          <t>누군가를 위해 곁에 있어주다, 돕다</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Okay, Rachel you’re up first.</t>
+          <t>when you ran out of your wedding, I was there for you.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Who's up first for the presentation? I think it's Sarah.</t>
+          <t>She was always there for me during my difficult times.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENG-20260529-025</t>
+          <t>ENG-20260529-120</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1609,39 +1609,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>run out on</t>
+          <t>put a roof over someone's head</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>/rʌn aʊt ɒn/</t>
+          <t>/pʊt ə ruːf ˈoʊvər ˈsʌmwʌnz hɛd/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>무책임하게 ~를 버리고 떠나다, ~를 외면하다</t>
+          <t>누군가에게 거처를 마련해주다, 재워주다</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>And also, I ran out on a wedding. You don’t get to keep the gifts.</t>
+          <t>I put a roof over your head</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>She felt completely abandoned after her business partner ran out on their joint venture.</t>
+          <t>My parents always made sure we had a roof over our heads, no matter what.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENG-20260529-026</t>
+          <t>ENG-20260529-121</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1656,39 +1656,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>draw on experience</t>
+          <t>not buy it</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>/drɔː ɒn ɪkˈspɪriəns/</t>
+          <t>/nɒt baɪ ɪt/</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경험을 활용하다, 경험에서 얻은 지식을 이용하다</t>
+          <t>믿지 않다, 납득하지 않다</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Very good! Drawing on your own experience, I like that!</t>
+          <t>Rachel isn't buying it</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>The seasoned negotiator had to draw on years of experience to close the difficult deal.</t>
+          <t>He tried to tell me he was sick, but I didn't buy it; he looked perfectly fine.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENG-20260529-027</t>
+          <t>ENG-20260529-122</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>kiss ass</t>
+          <t>drag someone into a mess</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1713,29 +1713,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>/kɪs æs/</t>
+          <t>/dræɡ ˈsʌmwʌn ˈɪntuː ə mɛs/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>아첨하다, 아부하다 (매우 비격식적이고 다소 부정적인 의미)</t>
+          <t>누군가를 곤란한 상황에 끌어들이다</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Ugh, what a kiss ass.</t>
+          <t>(Phoebe stops her and drags her into the kitchen.)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>He's always complimenting the boss; everyone thinks he's just trying to kiss ass.</t>
+          <t>I don't want to drag you into this mess, so I'll handle it myself.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ENG-20260529-028</t>
+          <t>ENG-20260529-123</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>make a scene</t>
+          <t>be with someone</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1760,29 +1760,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>/meɪk ə siːn/</t>
+          <t>/biː wɪð ˈsʌmwʌn/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>공공장소에서 소란을 피우다, 시선을 끄는 행동을 하다</t>
+          <t>(말하는 것을) 이해하다, 동의하다</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wait a minute! She just made a scene in the middle of the ceremony!</t>
+          <t>OK, OK. I'm with you, Cheech.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Please don't make a scene in the restaurant; let's discuss this calmly.</t>
+          <t>I think I'm with you now; that explanation makes more sense.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ENG-20260529-029</t>
+          <t>ENG-20260529-124</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>give a speech</t>
+          <t>lose meaning</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1807,29 +1807,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>/ɡɪv ə spiːtʃ/</t>
+          <t>/luːz ˈmiːnɪŋ/</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>연설을 하다</t>
+          <t>의미를 잃다</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It is time for you to give your maid of honor speech.</t>
+          <t>The word has lost all meaning.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>The CEO will give a speech at the annual company dinner next month.</t>
+          <t>After hearing it so many times, the phrase started to lose meaning.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ENG-20260529-030</t>
+          <t>ENG-20260529-125</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1844,39 +1844,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>never mind</t>
+          <t>wave off</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>/ˈnɛvər maɪnd/</t>
+          <t>/weɪv ɒf/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>신경 쓰지 마세요, 잊어버리세요, 상관 마세요</t>
+          <t>(생각, 제안 등을) 일축하다, (위험을) 물리치다</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Okay!! Forget that! That sucks!! Okay, never mind! Forget it!</t>
+          <t>Monica waves it off as though she doesn't believe it.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Oh, you found it? Never mind, I already bought a new one.</t>
+          <t>He tried to offer an excuse, but I just waved it off.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ENG-20260529-031</t>
+          <t>ENG-20260529-126</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>raise one's glass</t>
+          <t>spoil an appetite</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,29 +1901,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>/reɪz wʌnz ɡlɑːs/</t>
+          <t>/spɔɪl ən ˈæpɪtaɪt/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>건배를 제의하며 잔을 들어 올리다</t>
+          <t>식욕을 떨어뜨리다</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>So I would like to raise my glass to Monica and Chandler and the beautiful adventure they are about to embark upon together.</t>
+          <t>You don't want to spoil your appetite.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>At the reception, the best man raised his glass and offered a heartfelt toast to the happy couple.</t>
+          <t>Don't eat too much candy, you'll spoil your appetite for dinner.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENG-20260529-032</t>
+          <t>ENG-20260529-127</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>embark on/upon</t>
+          <t>bend down</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1948,29 +1948,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>/ɪmˈbɑːrk ɒn/ /ɪmˈbɑːrk əˈpɒn/</t>
+          <t>/bɛnd daʊn/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>새로운 일, 여행, 모험 등을 시작하다</t>
+          <t>몸을 숙이다, 허리를 굽히다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>So I would like to raise my glass to Monica and Chandler and the beautiful adventure they are about to embark upon together.</t>
+          <t>(When she bends down to pick it up he grabs a package of Gummi-bears)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>After graduation, she decided to embark on a round-the-world trip.</t>
+          <t>He had to bend down to tie his shoelaces.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ENG-20260529-033</t>
+          <t>ENG-20260529-128</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1985,39 +1985,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>be back in the game</t>
+          <t>pick up</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>/bi bæk ɪn ðə ɡeɪm/</t>
+          <t>/pɪk ʌp/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>활동이나 경쟁에 다시 참여하다, 회복하여 다시 기회가 생기다</t>
+          <t>~을 집어 들다, (물건을) 줍다</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Joey: And she’s back in the game.</t>
+          <t>she bends down to pick it up</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>After recovering from his injury, the athlete is eager to be back in the game next season.</t>
+          <t>Could you pick up the dry cleaning on your way home?</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ENG-20260529-034</t>
+          <t>ENG-20260529-129</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2032,39 +2032,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>owe an apology</t>
+          <t>get something out of the way</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>/oʊ æn əˈpɒlədʒi/</t>
+          <t>/ɡɛt ˈsʌmθɪŋ aʊt əv ðə weɪ/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>사과해야 할 의무가 있다, 사과할 일이 있다</t>
+          <t>성가신 일을 해치우다, 미리 처리하다</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ah, uh, I owe you a long overdue apology.</t>
+          <t>I need to get this report out of the way before I can relax.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>I realized I was wrong, and I definitely owe him an apology for my behavior.</t>
+          <t>Let's get the difficult conversation out of the way first.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ENG-20260529-035</t>
+          <t>ENG-20260529-130</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2074,44 +2074,44 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>demand a recount</t>
+          <t>go through the roof</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>/dɪˈmænd ə ˈriːkaʊnt/</t>
+          <t>/ɡoʊ θruː ðə ruːf/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>재검표를 요구하다</t>
+          <t>(가격, 수치 등이) 최고조에 달하다, 급등하다; (화가 머리끝까지) 치밀어 오르다</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Well then I demand a recount!</t>
+          <t>Demand for the new product has gone through the roof.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>The candidate, losing by a very narrow margin, immediately demanded a recount of the votes.</t>
+          <t>Rent prices in the city have gone through the roof recently.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ENG-20260529-036</t>
+          <t>ENG-20260529-131</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2121,44 +2121,44 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>flip a coin</t>
+          <t>level the playing field</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>idiom</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>/flɪp ə kɔɪn/</t>
+          <t>/ˈlɛvl̩ ðə ˈpleɪɪŋ fiːld/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>동전을 던져 결정하다, 운에 맡기다</t>
+          <t>경쟁 환경을 공정하게 만들다, 공평한 기회를 제공하다</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>We’re gonna flip a coin! All right?!</t>
+          <t>The new regulations are designed to level the playing field for all businesses.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Since we can't agree, let's just flip a coin to decide who goes first.</t>
+          <t>Access to education helps level the playing field for children from all backgrounds.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ENG-20260529-037</t>
+          <t>ENG-20260529-132</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2168,44 +2168,44 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>grunt in disgust</t>
+          <t>turn around</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>/ɡrʌnt ɪn dɪsˈɡʌst/</t>
+          <t>/tɜːrn əˈraʊnd/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>혐오감이나 불쾌감을 표현하며 끙 소리를 내다</t>
+          <t>(상황, 회사 등을) 호전시키다, 개선하다</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Looks at the coin and grunts in disgust.</t>
+          <t>The new CEO was hired to turn around the struggling company.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>He grunted in disgust when he saw the mess his roommates had left in the kitchen.</t>
+          <t>It took a lot of effort to turn around the failing project.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENG-20260529-038</t>
+          <t>ENG-20260529-133</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2215,44 +2215,44 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>throw a shower</t>
+          <t>be up against</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>/θroʊ ə ˈʃaʊər/</t>
+          <t>/biː ʌp əˈɡɛnst/</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>아기나 신부를 위한 파티(베이비샤워/브라이덜샤워)를 열어주다</t>
+          <t>(어려움, 경쟁자 등에) 직면하다, 맞서다</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>I hope Monica forgives you after you throw her, her vegetarian, voodoo, goddess circley shower!</t>
+          <t>We're up against a tight deadline, so we need to work efficiently.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Her friends are planning to throw her a surprise baby shower next month.</t>
+          <t>The new startup is up against some major established companies.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENG-20260529-039</t>
+          <t>ENG-20260529-134</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>be in the red/black</t>
+          <t>be out of line</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2277,29 +2277,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>/bi ɪn ðə rɛd/ /bi ɪn ðə blæk/</t>
+          <t>/biː aʊt ɒv laɪn/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>적자이다/흑자이다 (재정 상태를 나타냄)</t>
+          <t>도를 넘다, 무례하다, 부적절하다</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>After a difficult quarter, the company is finally in the black, showing a modest profit.</t>
+          <t>His comments in the meeting were completely out of line.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Many small businesses were in the red for months during the economic downturn.</t>
+          <t>You were out of line asking such personal questions.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENG-20260529-040</t>
+          <t>ENG-20260529-135</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sign off on</t>
+          <t>back out</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2324,29 +2324,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>/saɪn ɒf ɒn/</t>
+          <t>/bæk aʊt/</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>공식적으로 승인하다, 서명하여 허가하다</t>
+          <t>(약속, 계약 등에서) 발을 빼다, 취소하다</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The manager needs to sign off on all major expenditures before they are processed.</t>
+          <t>He promised to help, but he backed out at the last minute.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Before we proceed, we need the client to sign off on the design proposal.</t>
+          <t>Don't back out of the deal now; we've come too far.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENG-20260529-041</t>
+          <t>ENG-20260529-136</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2356,44 +2356,44 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>get buy-in</t>
+          <t>bring up</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>/ɡɛt ˈbaɪ ɪn/</t>
+          <t>/brɪŋ ʌp/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>지지나 동의를 얻다 (특히 중요한 결정이나 프로젝트에 대해)</t>
+          <t>(문제, 주제를) 제기하다, 꺼내다</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>It's crucial to get buy-in from all stakeholders before launching such a large-scale initiative.</t>
+          <t>I didn't want to bring up the sensitive topic during dinner.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>We need to present a strong case to the team if we want to get their buy-in for this new strategy.</t>
+          <t>She decided to bring up her concerns at the staff meeting.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENG-20260529-042</t>
+          <t>ENG-20260529-137</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2403,44 +2403,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>table a motion/discussion</t>
+          <t>end up</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>/ˈteɪbl ə ˈmoʊʃən/ /dəˈskʌʃən/</t>
+          <t>/ɛnd ʌp/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>논의를 나중으로 미루다 (영국 영어에서는 제안하다는 의미도 있음, 미국 영어에서는 보통 연기하다)</t>
+          <t>결국 ~하게 되다, ~로 끝나다</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Due to time constraints, the committee decided to table the discussion until the next meeting.</t>
+          <t>After all that planning, we ended up staying home anyway.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>I suggest we table this motion and revisit it after we gather more data.</t>
+          <t>If you don't study, you might end up failing the exam.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENG-20260529-043</t>
+          <t>ENG-20260529-138</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2450,44 +2450,44 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>put something on the back burner</t>
+          <t>hold off</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>/pʊt ˌsʌmθɪŋ ɒn ðə bæk ˈbɜːrnər/</t>
+          <t>/hoʊld ɒf/</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>덜 중요하거나 시급하지 않은 일로 미루다, 보류하다</t>
+          <t>~을 미루다, 보류하다</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>We had to put the new product development on the back burner to focus on our core business.</t>
+          <t>Let's hold off making a decision until we have all the facts.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>My personal projects have been put on the back burner while I deal with urgent work.</t>
+          <t>They decided to hold off on their travel plans due to the bad weather.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENG-20260529-044</t>
+          <t>ENG-20260529-139</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2502,39 +2502,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>go public</t>
+          <t>look into</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>/ɡoʊ ˈpʌblɪk/</t>
+          <t>/lʊk ˈɪntuː/</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>회사 주식을 공개적으로 발행하여 상장하다</t>
+          <t>~을 조사하다, 검토하다</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Many startups dream of the day they can go public and offer shares to the public.</t>
+          <t>The company is looking into the possibility of expanding into new markets.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>After years of growth, the successful tech company decided to go public last month.</t>
+          <t>We're looking into the cause of the system error.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENG-20260529-045</t>
+          <t>ENG-20260529-140</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>crunch numbers</t>
+          <t>set up</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>/krʌntʃ ˈnʌmbərz/</t>
+          <t>/sɛt ʌp/</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>복잡한 계산을 하다, 데이터를 분석하다</t>
+          <t>~을 설치하다, 마련하다; (사업 등을) 시작하다</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The finance department is busy crunching numbers to prepare the annual budget report.</t>
+          <t>We need to set up a new meeting room for the presentation.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>She spends hours every day crunching numbers to identify market trends.</t>
+          <t>They plan to set up a new branch office in London.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENG-20260529-046</t>
+          <t>ENG-20260529-141</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2591,44 +2591,44 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>trim the fat</t>
+          <t>put up with</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>/trɪm ðə fæt/</t>
+          <t>/pʊt ʌp wɪð/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>불필요한 비용이나 부분을 줄이다, 낭비를 없애다</t>
+          <t>~을 참다, 견디다</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>To improve profitability, the company needs to trim the fat from its operational budget.</t>
+          <t>I don't know how she puts up with his constant complaining.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>We're trying to trim the fat from our monthly expenses so we can save more.</t>
+          <t>He had to put up with a lot of noise from his neighbors.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENG-20260529-047</t>
+          <t>ENG-20260529-142</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2643,39 +2643,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>be in a pickle</t>
+          <t>count on</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>/bi ɪn ə ˈpɪkl/</t>
+          <t>/kaʊnt ɒn/</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>곤란한 상황에 처하다, 궁지에 몰리다</t>
+          <t>~을 믿다, 의지하다</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>We're really in a pickle now that we missed the deadline and haven't finished the report.</t>
+          <t>You can always count on me for support.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>If we don't find a solution soon, we're going to be in a real pickle.</t>
+          <t>I'm counting on you to help me with this project.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENG-20260529-048</t>
+          <t>ENG-20260529-143</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2690,39 +2690,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>pass with flying colors</t>
+          <t>look forward to</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>/pæs wɪð ˈflaɪɪŋ ˈkʌlərz/</t>
+          <t>/lʊk ˈfɔːrwərd tuː/</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>시험이나 과제를 아주 훌륭하게 통과하다, 성공적으로 해내다</t>
+          <t>~을 고대하다, 기대하다</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>She studied diligently for weeks and passed her final exams with flying colors.</t>
+          <t>I'm really looking forward to seeing you next week.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Despite the difficulty, he passed the driving test with flying colors on his first attempt.</t>
+          <t>We're looking forward to our summer vacation.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENG-20260529-049</t>
+          <t>ENG-20260529-144</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2737,39 +2737,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pull oneself together</t>
+          <t>show up</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>/pʊl wʌnˈsɛlf təˈɡɛðər/</t>
+          <t>/ʃoʊ ʌp/</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>감정을 추스르다, 마음을 가다듬다</t>
+          <t>나타나다, 모습을 드러내다</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>After a brief moment of panic, she managed to pull herself together and solve the problem calmly.</t>
+          <t>He said he would be here at 7, but he never showed up.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Come on, pull yourself together! We need to focus on finding a solution.</t>
+          <t>I hope everyone shows up for the meeting on time.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENG-20260529-050</t>
+          <t>ENG-20260529-145</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2784,39 +2784,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>get a kick out of</t>
+          <t>work out</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>/ɡɛt ə kɪk aʊt ɒv/</t>
+          <t>/wɜːrk aʊt/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>~로부터 큰 즐거움이나 흥분을 느끼다</t>
+          <t>잘 풀리다, 성공하다; 운동하다; (문제를) 해결하다</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He really gets a kick out of surprising people with unexpected gifts.</t>
+          <t>I hope everything works out for you.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>I always get a kick out of watching old comedy shows like Friends.</t>
+          <t>Don't worry, I'm sure it will all work out in the end.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENG-20260529-051</t>
+          <t>ENG-20260529-146</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2826,44 +2826,44 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>be glued to</t>
+          <t>break down</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>/bi ɡluːd tuː/</t>
+          <t>/breɪk daʊn/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>어떤 것에 시선이나 주의를 고정시키다, 몰두하다</t>
+          <t>고장 나다; (협상 등이) 결렬되다; (울음을) 터뜨리다</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kids nowadays are constantly glued to their screens, whether it's a phone or a tablet.</t>
+          <t>The car broke down on the highway, so we had to call for a tow.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>I was glued to the TV, watching the breaking news report about the rocket launch.</t>
+          <t>Negotiations between the two countries broke down without an agreement.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENG-20260529-052</t>
+          <t>ENG-20260529-147</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>hang in there</t>
+          <t>fill in</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2888,29 +2888,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>/hæŋ ɪn ðɛər/</t>
+          <t>/fɪl ɪn/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>어려운 상황에서도 포기하지 않고 버티다, 힘내다</t>
+          <t>(빈칸을) 채우다; (정보를) 알려주다</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>I know things are tough right now, but just hang in there; it'll get better.</t>
+          <t>Can you fill me in on what I missed during the meeting?</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Hang in there, you're almost done with this challenging project!</t>
+          <t>I'll fill you in on the details later.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENG-20260529-053</t>
+          <t>ENG-20260529-148</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2925,39 +2925,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>let someone off the hook</t>
+          <t>hold on</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>/lɛt ˌsʌmwʌn ɒf ðə hʊk/</t>
+          <t>/hoʊld ɒn/</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>누군가를 어려운 상황이나 처벌에서 벗어나게 해주다</t>
+          <t>기다리다; 버티다</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Even though he broke the rules, the teacher decided to let him off the hook this time.</t>
+          <t>Hold on a minute, I'll be right back.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>I'll let you off the hook for washing dishes tonight since you've had a long day.</t>
+          <t>Can you hold on for a moment while I check?</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENG-20260529-054</t>
+          <t>ENG-20260529-149</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2972,39 +2972,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ring a bell</t>
+          <t>put down</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>/rɪŋ ə bɛl/</t>
+          <t>/pʊt daʊn/</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>익숙하거나 들어본 적이 있는 것 같다, 기억나게 하다</t>
+          <t>~을 내려놓다; (누군가를) 비하하다, 폄하하다</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>His name rings a bell, but I can't quite remember where I know him from.</t>
+          <t>Please put down your phone while we're talking.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>That song title sounds familiar; it definitely rings a bell.</t>
+          <t>It's not right to put down other people's ideas.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENG-20260529-055</t>
+          <t>ENG-20260529-150</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3014,44 +3014,44 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>HBR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>see eye to eye</t>
+          <t>take apart</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>/siː aɪ tuː aɪ/</t>
+          <t>/teɪk əˈpɑːrt/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>의견이 일치하다, 동의하다</t>
+          <t>~을 분해하다; (계획 등을) 철저히 분석하다</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>My brother and I rarely see eye to eye on political matters, but we respect each other's opinions.</t>
+          <t>The engineer took apart the machine to find the fault.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>It's difficult to work with him because we just don't see eye to eye on anything.</t>
+          <t>We need to take apart the competitor's strategy to understand their success.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENG-20260529-056</t>
+          <t>ENG-20260529-151</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>brace oneself</t>
+          <t>turn up</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>/breɪs wʌnˈsɛlf/</t>
+          <t>/tɜːrn ʌp/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>힘든 일이나 충격에 대비하다, 마음의 준비를 하다</t>
+          <t>나타나다; (소리, 불빛 등을) 높이다; (예상치 않게) 발견되다</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Everyone had to brace themselves for the severe storm expected to hit the coast.</t>
+          <t>He finally turned up at the party after midnight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>We need to brace ourselves for a challenging quarter with potentially lower sales.</t>
+          <t>Could you please turn up the volume?</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENG-20260529-057</t>
+          <t>ENG-20260529-152</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3113,39 +3113,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>pat oneself on the back</t>
+          <t>break up</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>/pæt wʌnˈsɛlf ɒn ðə bæk/</t>
+          <t>/breɪk ʌp/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>자신을 칭찬하다, 스스로에게 잘했다고 하다</t>
+          <t>(관계가) 끝나다, 헤어지다</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>After successfully completing the difficult project, the team could finally pat themselves on the back.</t>
+          <t>They broke up after dating for five years.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>You did a fantastic job on that presentation; you should definitely pat yourself on the back.</t>
+          <t>It's always sad when a band breaks up.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENG-20260529-058</t>
+          <t>ENG-20260529-153</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3160,39 +3160,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>knock it out of the park</t>
+          <t>get away with</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>/nɒk ɪt aʊt ɒv ðə pɑːrk/</t>
+          <t>/ɡɛt əˈweɪ wɪð/</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>기대 이상으로 아주 잘 해내다, 대성공을 거두다 (야구 용어에서 유래)</t>
+          <t>(처벌 없이) ~을 모면하다</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Her performance in the play was truly exceptional; she really knocked it out of the park.</t>
+          <t>He cheated on the exam and got away with it.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>I'm confident the sales team will knock it out of the park with this new product.</t>
+          <t>You can't just break the rules and expect to get away with it.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENG-20260529-059</t>
+          <t>ENG-20260529-154</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3202,44 +3202,44 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>get on board</t>
+          <t>keep up with</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>/ɡɛt ɒn bɔːrd/</t>
+          <t>/kiːp ʌp wɪð/</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>어떤 계획, 아이디어 등에 동의하거나 참여하다</t>
+          <t>~에 뒤처지지 않다, ~을 따라잡다</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>It was difficult to get all the team members on board with the radical new proposal.</t>
+          <t>It's hard to keep up with all the latest technology.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>We need everyone to get on board with this new initiative if we want it to succeed.</t>
+          <t>She studies hard to keep up with her classmates.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENG-20260529-060</t>
+          <t>ENG-20260529-155</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3249,44 +3249,44 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>put one's cards on the table</t>
+          <t>look out for</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>/pʊt wʌnz kɑːrdz ɒn ðə ˈteɪbl/</t>
+          <t>/lʊk aʊt fɔːr/</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>자신의 계획이나 의도를 솔직하게 밝히다</t>
+          <t>~을 조심하다; ~을 찾아주다, 보살피다</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>During the negotiation, both sides agreed to put their cards on the table to find a fair solution.</t>
+          <t>Look out for pickpockets in crowded areas.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Let's put our cards on the table and discuss our expectations openly.</t>
+          <t>Could you look out for my luggage while I get a coffee?</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENG-20260529-061</t>
+          <t>ENG-20260529-156</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3296,44 +3296,44 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>nip something in the bud</t>
+          <t>pull through</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>/nɪp ˌsʌmθɪŋ ɪn ðə bʌd/</t>
+          <t>/pʊl θruː/</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>문제나 나쁜 상황이 더 커지기 전에 미리 막다</t>
+          <t>(병, 어려움 등을) 극복하다, 이겨내다</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>It's important to nip bad habits in the bud before they become ingrained.</t>
+          <t>We were worried, but she managed to pull through her illness.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>The manager intervened quickly to nip the disagreement in the bud before it escalated.</t>
+          <t>The company managed to pull through the financial crisis.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENG-20260529-062</t>
+          <t>ENG-20260529-157</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>pay through the nose</t>
+          <t>run out</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>/peɪ θruː ðə noʊz/</t>
+          <t>/rʌn aʊt/</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>터무니없이 비싼 값을 지불하다, 바가지를 쓰다</t>
+          <t>(시간, 공급 등이) 다 되다, 소진되다</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>I hate having to pay through the nose for basic necessities like groceries these days.</t>
+          <t>Time is running out, so we need to make a decision soon.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>We had to pay through the nose for tickets to the concert because we bought them last minute.</t>
+          <t>We've almost run out of patience with their excuses.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENG-20260529-063</t>
+          <t>ENG-20260529-158</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3390,44 +3390,44 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>word of mouth</t>
+          <t>walk out</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>/wɜːrd ɒv maʊθ/</t>
+          <t>/wɔːk aʊt/</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>입소문, 구전</t>
+          <t>떠나다, (시위하며) 퇴장하다</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Most of our new customers come to us through word of mouth referrals.</t>
+          <t>The employees threatened to walk out if their demands were not met.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>The restaurant became popular largely through positive word of mouth from local food bloggers.</t>
+          <t>She was so angry she just walked out of the room.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENG-20260529-064</t>
+          <t>ENG-20260529-159</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>keep one's options open</t>
+          <t>on track</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3452,29 +3452,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>/kiːp wʌnz ˈɒpʃənz ˈoʊpən/</t>
+          <t>/ɑn træk/</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>결정을 내리지 않고 여러 가능성을 열어두다</t>
+          <t>순조롭게 진행 중인, 예정대로</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>It's wise to keep your options open when you're looking for a new job.</t>
+          <t>it is on track to hit the regulator Ofcom's reduced targets</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>I'm applying to several universities to keep my options open.</t>
+          <t>The construction project is on track to be completed by next month.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENG-20260529-065</t>
+          <t>ENG-20260529-160</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3489,39 +3489,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>be up to scratch</t>
+          <t>face job shortage</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>/bi ʌp tuː skrætʃ/</t>
+          <t>/feɪs dʒɑb ˈʃɔrtɪdʒ/</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>기대에 부응하다, 필요한 수준에 미치다 (주로 부정문에 사용)</t>
+          <t>일자리 부족에 직면하다</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>His recent work hasn't been up to scratch, so he needs to improve.</t>
+          <t>how young people are facing the job shortage</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The quality of the product wasn't up to scratch, so we returned it.</t>
+          <t>In some rural areas, residents often face job shortage due to limited industries.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENG-20260529-066</t>
+          <t>ENG-20260529-161</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>BBC_Business</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>blow something out of proportion</t>
+          <t>north of the border</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3546,29 +3546,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>/bloʊ ˌsʌmθɪŋ aʊt ɒv prəˈpɔːrʃən/</t>
+          <t>/nɔrθ əv ðə ˈbɔrdər/</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>사소한 일을 과장하다, 침소봉대하다</t>
+          <t>국경 북쪽에서 (주로 캐나다와 미국 사이에서 쓰임), (비유적으로) 특정 기준 이상</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>It was just a minor disagreement, but she blew it out of proportion and made a huge fuss.</t>
+          <t>had plummetted north of the border</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Don't blow this small mistake out of proportion; it's easily fixable.</t>
+          <t>Many Canadians travel south for shopping, but some prefer to find unique items north of the border.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENG-20260529-067</t>
+          <t>ENG-20260529-162</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3583,39 +3583,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>butter someone up</t>
+          <t>rush to explain</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>phrasal verb</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>/ˈbʌtər ˌsʌmwʌn ʌp/</t>
+          <t>/rʌʃ tu ɪkˈspleɪn/</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>누군가에게 아첨하다, 환심을 사려고 노력하다</t>
+          <t>급하게 설명하다</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>He tried to butter up his boss before asking for a raise.</t>
+          <t>Ross: (rushing to explain) Funny story!</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>She's always buttering up her professors to get better grades.</t>
+          <t>When he realized his mistake, he rushed to explain the situation to his boss.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENG-20260529-068</t>
+          <t>ENG-20260529-163</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3630,39 +3630,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>in the blink of an eye</t>
+          <t>overhear a conversation</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>/ɪn ðə blɪŋk ɒv æn aɪ/</t>
+          <t>/ˌoʊvərˈhɪər ə ˌkɑnvərˈseɪʃən/</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>눈 깜짝할 사이에, 순식간에</t>
+          <t>대화를 엿듣다, 우연히 듣다</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>The entire building was engulfed in flames in the blink of an eye.</t>
+          <t>Rachel walks in and overhears the conversation.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>The car disappeared around the corner in the blink of an eye.</t>
+          <t>I accidentally overheard a conversation between my neighbors about their vacation plans.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENG-20260529-069</t>
+          <t>ENG-20260529-164</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3677,39 +3677,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>jump to conclusions</t>
+          <t>have a deal</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>/dʒʌmp tuː kənˈkluːʒənz/</t>
+          <t>/hæv ə dil/</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>성급하게 결론을 내리다, 속단하다</t>
+          <t>합의가 되다, 거래가 성사되다</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Don't jump to conclusions; let's wait for all the facts before making a judgment.</t>
+          <t>Wendy, we had a deal!</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>I know you're upset, but try not to jump to conclusions about what happened.</t>
+          <t>After weeks of discussion, we finally have a deal on the new contract.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENG-20260529-070</t>
+          <t>ENG-20260529-165</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3724,39 +3724,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>live and learn</t>
+          <t>hang up</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>/lɪv ænd lɜːrn/</t>
+          <t>/hæŋ ʌp/</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>실수를 통해 배우다, 경험을 통해 성장하다</t>
+          <t>(전화를) 끊다</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>I made a big mistake, but I guess you live and learn.</t>
+          <t>(hangs up)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>I accidentally booked flights for the wrong date, but hey, live and learn.</t>
+          <t>Please don't hang up, I need to tell you something important.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ENG-20260529-071</t>
+          <t>ENG-20260529-166</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3771,39 +3771,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>pull strings</t>
+          <t>drag someone into</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>/pʊl strɪŋz/</t>
+          <t>/dræɡ ˈsʌmˌwʌn ˈɪntu/</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>뒷배경을 이용하다, 인맥을 동원하다 (주로 부정적 의미)</t>
+          <t>(~을) 강제로 끌어들이다, 억지로 참여시키다</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>He managed to get that exclusive invitation by pulling some strings with influential people.</t>
+          <t>Phoebe stops her and drags her into the kitchen.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>She had to pull some strings to get her son into that prestigious school.</t>
+          <t>He didn't want to get involved, but his friends dragged him into the argument.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ENG-20260529-072</t>
+          <t>ENG-20260529-167</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rags to riches</t>
+          <t>on the way over</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3828,29 +3828,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>/ræɡz tuː ˈrɪtʃɪz/</t>
+          <t>/ɑn ðə weɪ ˈoʊvər/</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>극빈층에서 부유층으로 성공하다, 자수성가하다</t>
+          <t>오는 길에, (어떤 곳으로) 가는 도중에</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>His rags to riches story is an inspiration to many aspiring entrepreneurs.</t>
+          <t>In the cab, on the way over, Steve blazed up a doobie.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Many successful entrepreneurs have a rags to riches story.</t>
+          <t>I'll pick up some snacks on the way over to your place.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENG-20260529-073</t>
+          <t>ENG-20260529-168</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3860,44 +3860,44 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BBC_Business</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>red tape</t>
+          <t>blaze up</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>/rɛd teɪp/</t>
+          <t>/bleɪz ʌp/</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>불필요하게 복잡하고 관료적인 절차, 관료주의</t>
+          <t>(담배, 특히 마리화나를) 피우다</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>It took months to get the permits due to excessive red tape and bureaucratic hurdles.</t>
+          <t>Steve blazed up a doobie.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Dealing with all the government red tape for a small business loan was frustrating.</t>
+          <t>He tried to blaze up a cigarette discreetly in the alley.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ENG-20260529-074</t>
+          <t>ENG-20260529-169</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>up to par</t>
+          <t>light a bone</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3922,29 +3922,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>/ʌp tuː pɑːr/</t>
+          <t>/laɪt ə boʊn/</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>기대하는 수준에 미치다, 보통 수준에 달하다</t>
+          <t>(마리화나) 한 대 피우다 (속어)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>His performance hasn't been up to par recently, and he needs to improve.</t>
+          <t>You know, lit a bone?</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>The new restaurant's service wasn't quite up to par yet.</t>
+          <t>After a long day, some people might want to light a bone to relax.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ENG-20260529-075</t>
+          <t>ENG-20260529-170</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3954,44 +3954,44 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HBR</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>win-win situation</t>
+          <t>bring over</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>collocation</t>
+          <t>phrasal verb</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>/wɪn wɪn ˌsɪtʃuˈeɪʃən/</t>
+          <t>/brɪŋ ˈoʊvər/</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>모두에게 이득이 되는 상황, 상생 관계</t>
+          <t>(~을) 가져오다, 데려오다</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>The new partnership is a win-win situation for both companies involved.</t>
+          <t>Monica brings over a tray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Working from home is a win-win situation for both employees and employers.</t>
+          <t>Can you bring over the documents I left on my desk?</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENG-20260529-076</t>
+          <t>ENG-20260529-171</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>call it a night</t>
+          <t>one by one</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4016,29 +4016,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>/kɔːl ɪt ə naɪt/</t>
+          <t>/wʌn baɪ wʌn/</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>그날 밤의 활동을 끝내다, 귀가하다</t>
+          <t>하나씩, 차례로</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It's late, so let's call it a night and pick this up tomorrow.</t>
+          <t>Steve starts to eat them one by one, quickly</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>After a long evening out, we decided to call it a night.</t>
+          <t>The children opened their presents one by one on Christmas morning.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENG-20260529-077</t>
+          <t>ENG-20260529-172</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4053,39 +4053,39 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>come rain or shine</t>
+          <t>with a touch of</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>/kʌm reɪn ɔːr ʃaɪn/</t>
+          <t>/wɪð ə tʌtʃ əv/</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>날씨가 어떻든, 어떤 어려움이 있든 상관없이, 무슨 일이 있어도</t>
+          <t>약간의 (~을 곁들여), 조금의 (~을 더해)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>I'll be there for you, come rain or shine, no matter what happens.</t>
+          <t>with just a touch of mints</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>The outdoor festival will proceed come rain or shine.</t>
+          <t>The dish was perfect, with a touch of garlic and fresh herbs.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ENG-20260529-078</t>
+          <t>ENG-20260529-173</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4100,39 +4100,39 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>down to earth</t>
+          <t>get someone's attention</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>/daʊn tuː ɜːrθ/</t>
+          <t>/ɡɛt ˈsʌmˌwʌnz əˈtɛnʃən/</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>현실적인, 실용적인, 소탈한</t>
+          <t>(~의) 주의를 끌다</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Despite her fame, she's very down to earth and easy to talk to.</t>
+          <t>Rachel tries to get Monica's attention</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>I appreciate his down to earth approach to problem-solving.</t>
+          <t>She tried waving her hands to get the waiter's attention.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ENG-20260529-079</t>
+          <t>ENG-20260529-174</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4147,39 +4147,39 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>easy come, easy go</t>
+          <t>drag on a joint</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>/ˈiːzi kʌm ˈiːzi ɡoʊ/</t>
+          <t>/dræɡ ɑn ə dʒɔɪnt/</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>쉽게 얻은 것은 쉽게 사라진다</t>
+          <t>(마리화나) 한 모금 피우다 (속어)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>He won a large sum of money but spent it all quickly. Easy come, easy go.</t>
+          <t>She pretends to drag on a joint</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>I lost my lottery winnings quickly; easy come, easy go, I suppose.</t>
+          <t>He quietly took a drag on his cigarette before going inside.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENG-20260529-080</t>
+          <t>ENG-20260529-175</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4189,742 +4189,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>get wind of</t>
+          <t>give the OK signal</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>idiom</t>
+          <t>collocation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>/ɡɛt wɪnd ɒv/</t>
+          <t>/ɡɪv ðɪ oʊˈkeɪ ˈsɪɡnəl/</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>소문을 듣다, ~에 대해 알게 되다</t>
+          <t>승인 신호를 주다, 괜찮다는 신호를 보내다</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The competitors got wind of our new product launch plans.</t>
+          <t>Monica thinks she's giving her the 'OK' signal.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>The press got wind of the scandal before the official announcement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ENG-20260529-081</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HBR</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>in a nutshell</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>/ɪn ə ˈnʌtʃɛl/</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>아주 간단히 말해서, 요약하자면</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>In a nutshell, the company is facing financial difficulties due to mismanagement.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>In a nutshell, we need to increase sales and reduce costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>ENG-20260529-082</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Friends</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>it's not rocket science</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>/ɪts nɒt ˈrɒkɪt ˈsaɪəns/</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>그리 어려운 일이 아니다 (로켓 과학처럼 복잡하지 않다는 뜻)</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Learning to use this new software is not rocket science; anyone can do it.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Figuring out how to use the coffee machine is not rocket science.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>ENG-20260529-083</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Friends</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>know something like the back of one's hand</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>/noʊ ˌsʌmθɪŋ laɪk ðə bæk ɒv wʌnz hænd/</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>무언가를 아주 잘 알다, 꿰뚫어보다</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>She's lived in this city her whole life, so she knows it like the back of her hand.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>I've worked in this department for years; I know this system like the back of my hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>ENG-20260529-084</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>HBR</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>on the ball</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>/ɒn ðə bɔːl/</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>유능한, 기민한, 상황을 잘 파악하고 있는</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>You need to be on the ball to succeed in a fast-paced environment like this.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Our new project manager is really on the ball; nothing gets past her.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>ENG-20260529-085</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HBR</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>the big picture</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>/ðə bɪɡ ˈpɪktʃər/</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>전체적인 상황, 전체적인 그림</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Don't get too caught up in the details; try to look at the big picture.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>He's good at seeing the big picture and understanding how all the parts fit together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>ENG-20260529-086</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>BBC_Business</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>work one's fingers to the bone</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>/wɜːrk wʌnz ˈfɪŋɡərz tuː ðə boʊn/</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>뼈 빠지게 일하다, 매우 열심히 일하다</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>She worked her fingers to the bone to provide for her family.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Many entrepreneurs work their fingers to the bone to get their businesses off the ground.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>ENG-20260529-087</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>make a determination</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>/meɪk ə dɪˌtɜːrmɪˈneɪʃən/</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>결정을 내리다, 확정하다</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Trump lays out Iran deal demands, says he's about to make 'final determination'</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>The committee will make a final determination on the proposal next week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ENG-20260529-088</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>cover expenses</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>/ˈkʌvər ɪkˈspɛnsɪz/</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>비용을 충당하다</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Higher energy costs can force consumers to raid their savings and lean more into debt to cover expenses.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Many students work part-time jobs to cover their living expenses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ENG-20260529-089</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>pace of growth</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>/peɪs əv ɡroʊθ/</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>성장 속도</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Dell reported its fastest pace of revenue growth since returning to the public market in 2018, with AI server revenue soaring 757% over last year.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>The company needs to maintain a high pace of growth to attract investors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ENG-20260529-090</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>file for renewal</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>/faɪl fɔːr rɪˈnuːəl/</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>갱신 신청을 하다</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Disney's ABC files early broadcast licenses renewal. FCC Chair vows to 'follow the facts'</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>You must file for renewal of your passport before it expires.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ENG-20260529-091</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>follow the facts</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>/ˈfɑːloʊ ðə fækts/</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>사실에 입각하다, 사실을 따르다</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Disney's ABC files early broadcast licenses renewal. FCC Chair vows to 'follow the facts'</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>It's crucial for journalists to follow the facts and report objectively.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ENG-20260529-092</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>file under protest</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>idiom</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>/faɪl ˈʌndər ˈproʊtɛst/</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>이의를 제기하며 제출하다</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Disney said it filed renewals for eight broadcast station licenses 'under protest,' after the FCC launched an early review years ahead of schedule.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>The company decided to file the tax return under protest, reserving its right to challenge the assessment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>ENG-20260529-093</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>repay debt</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>/riːˈpeɪ dɛt/</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>빚을 갚다</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Starting July 1, millions of federal student loan holders will have two new ways to repay their debt.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>It's wise to create a budget to help you repay your debt more efficiently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>ENG-20260529-094</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>BBC_Business</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>hit targets</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>/hɪt ˈtɑːrɡɪts/</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>목표를 달성하다</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Royal Mail says its service is improving and that it is on track to hit the regulator Ofcom's reduced targets</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>The sales team worked hard to hit their quarterly targets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ENG-20260529-095</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>BBC_Business</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>mounting pressure</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>collocation</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>/ˈmaʊntɪŋ ˈprɛʃər/</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>가중되는 압력/부담</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Tom Kerridge, Yotam Ottolenghi, Ravneet Gill and Simon Rogan told BBC Newsnight VAT should be halved to ease mounting pressure on the hospitality industry.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>She felt mounting pressure to finish the project on time.</t>
+          <t>The director gave the OK signal, and the cameras started rolling.</t>
         </is>
       </c>
     </row>
